--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -52,14 +52,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0090EE90"/>
-        <bgColor rgb="0090EE90"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="0090EE90"/>
+        <bgColor rgb="0090EE90"/>
       </patternFill>
     </fill>
     <fill>
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -93,13 +93,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -479,7 +476,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -571,19 +568,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -623,19 +616,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
@@ -680,19 +669,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -735,19 +720,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -790,19 +771,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -811,7 +788,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -845,19 +822,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -866,7 +839,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>78</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8">
@@ -900,19 +873,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -955,19 +924,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -977,7 +942,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1012,19 +977,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1034,7 +995,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1069,19 +1030,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -1116,19 +1073,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -1163,19 +1116,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1215,19 +1164,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
@@ -1307,19 +1252,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1339,22 +1280,22 @@
         <v>20</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1389,19 +1330,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1421,22 +1358,22 @@
         <v>21</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1471,19 +1408,15 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1503,63 +1436,63 @@
         <v>21</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -1581,63 +1514,63 @@
         <v>21</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>12:05:00</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -1659,63 +1592,63 @@
         <v>20</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -1737,63 +1670,63 @@
         <v>20</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>17/01/2026</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -1815,22 +1748,22 @@
         <v>20</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1865,19 +1798,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -1897,22 +1826,22 @@
         <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1947,19 +1876,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -1979,22 +1904,22 @@
         <v>20</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2029,19 +1954,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -2061,22 +1982,22 @@
         <v>21</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2111,19 +2032,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -2143,22 +2060,22 @@
         <v>21</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2193,19 +2110,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -2225,22 +2138,22 @@
         <v>21</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2275,19 +2188,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -2357,19 +2266,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -2439,19 +2344,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -2491,43 +2392,43 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>06/01/2026</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -2569,43 +2470,43 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -2677,19 +2578,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -2759,19 +2656,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -2841,19 +2734,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -2893,43 +2782,43 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>19/01/2026</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -3001,19 +2890,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -3083,19 +2968,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -3165,19 +3046,15 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -3217,129 +3094,129 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>12:05:00</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -3351,43 +3228,43 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>17/01/2026</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -3439,27 +3316,23 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
           <t>Recorded</t>
         </is>
       </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="L43" s="6" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -3501,19 +3374,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
@@ -3521,7 +3390,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L44" s="7" t="inlineStr">
+      <c r="L44" s="6" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -3563,19 +3432,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
@@ -3583,7 +3448,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L45" s="8" t="inlineStr">
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3625,19 +3490,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3672,19 +3533,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3719,19 +3576,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3766,19 +3619,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3813,103 +3662,99 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>06/01/2026</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>0/18</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>0/18</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -3946,19 +3791,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3993,19 +3834,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4040,60 +3877,56 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>19/01/2026</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr"/>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>0/18</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -4130,19 +3963,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4177,19 +4006,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4224,189 +4049,185 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr"/>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>0/18</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>12:05:00</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr"/>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>0/18</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr"/>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>0/18</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>17/01/2026</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr"/>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>0/18</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -4443,19 +4264,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>18/21</t>
+          <t>0/21</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4490,19 +4307,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>18/21</t>
+          <t>0/21</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4537,19 +4350,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>14/21</t>
+          <t>0/21</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4584,19 +4393,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>20/21</t>
+          <t>0/21</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4631,19 +4436,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17/21</t>
+          <t>0/21</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4678,19 +4479,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>19/21</t>
+          <t>0/21</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4725,19 +4522,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>15/21</t>
+          <t>0/21</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4772,103 +4565,99 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17/21</t>
+          <t>0/21</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>06/01/2026</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr"/>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>0/21</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr"/>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>0/21</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -4905,19 +4694,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>20/21</t>
+          <t>0/21</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4952,19 +4737,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>16/21</t>
+          <t>0/21</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4999,60 +4780,56 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>11/21</t>
+          <t>0/21</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>19/01/2026</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>0/21</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -5089,19 +4866,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>17/21</t>
+          <t>0/21</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5136,19 +4909,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18/21</t>
+          <t>0/21</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5183,189 +4952,185 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18/21</t>
+          <t>0/21</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>0/21</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>12:05:00</t>
         </is>
       </c>
-      <c r="G82" s="5" t="inlineStr"/>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>0/21</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G83" s="5" t="inlineStr"/>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>0/21</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>17/01/2026</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G84" s="5" t="inlineStr"/>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>0/21</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -5402,19 +5167,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>30/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5449,19 +5210,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>29/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5496,19 +5253,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>29/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5543,19 +5296,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>30/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5590,19 +5339,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5637,19 +5382,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5684,19 +5425,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5731,19 +5468,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>29/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5778,19 +5511,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>30/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5825,19 +5554,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>31/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5872,19 +5597,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5919,19 +5640,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5966,19 +5683,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6013,19 +5726,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6060,19 +5769,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6107,189 +5812,185 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G101" s="5" t="inlineStr"/>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>12:05:00</t>
         </is>
       </c>
-      <c r="G102" s="5" t="inlineStr"/>
-      <c r="H102" s="5" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E103" s="5" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G103" s="5" t="inlineStr"/>
-      <c r="H103" s="5" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E104" s="5" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>17/01/2026</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="5" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I104" s="5" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -6326,19 +6027,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6373,19 +6070,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6420,19 +6113,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>27/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6467,19 +6156,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>27/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6514,19 +6199,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6561,19 +6242,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>28/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6608,19 +6285,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>28/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6655,19 +6328,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6702,19 +6371,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6749,19 +6414,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>27/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6796,19 +6457,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6843,19 +6500,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6890,19 +6543,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6937,19 +6586,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6984,19 +6629,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7031,189 +6672,185 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E121" s="5" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F121" s="5" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G121" s="5" t="inlineStr"/>
-      <c r="H121" s="5" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I121" s="5" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C122" s="5" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E122" s="5" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F122" s="5" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>12:05:00</t>
         </is>
       </c>
-      <c r="G122" s="5" t="inlineStr"/>
-      <c r="H122" s="5" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I122" s="5" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D123" s="5" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E123" s="5" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G123" s="5" t="inlineStr"/>
-      <c r="H123" s="5" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I123" s="5" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C124" s="5" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D124" s="5" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E124" s="5" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>17/01/2026</t>
         </is>
       </c>
-      <c r="F124" s="5" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G124" s="5" t="inlineStr"/>
-      <c r="H124" s="5" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I124" s="5" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -7250,19 +6887,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>29/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7297,19 +6930,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7344,19 +6973,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7391,19 +7016,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>29/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7438,19 +7059,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7485,19 +7102,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7532,19 +7145,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>29/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7579,19 +7188,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7626,19 +7231,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>28/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7673,19 +7274,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>28/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7720,19 +7317,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7767,19 +7360,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7814,19 +7403,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7861,19 +7446,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7908,19 +7489,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7955,189 +7532,185 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C141" s="5" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D141" s="5" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E141" s="5" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F141" s="5" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G141" s="5" t="inlineStr"/>
-      <c r="H141" s="5" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I141" s="5" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E142" s="5" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F142" s="5" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>12:05:00</t>
         </is>
       </c>
-      <c r="G142" s="5" t="inlineStr"/>
-      <c r="H142" s="5" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I142" s="5" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E143" s="5" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F143" s="5" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G143" s="5" t="inlineStr"/>
-      <c r="H143" s="5" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I143" s="5" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B144" s="5" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C144" s="5" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D144" s="5" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E144" s="5" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>17/01/2026</t>
         </is>
       </c>
-      <c r="F144" s="5" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G144" s="5" t="inlineStr"/>
-      <c r="H144" s="5" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I144" s="5" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -8174,19 +7747,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>32/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8221,19 +7790,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>29/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8268,19 +7833,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>31/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8315,19 +7876,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>32/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8362,19 +7919,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>30/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8409,19 +7962,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>32/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8456,19 +8005,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>33/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8503,19 +8048,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>28/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8550,19 +8091,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>30/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8597,19 +8134,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>33/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8644,19 +8177,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>26/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8691,19 +8220,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>22/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8738,19 +8263,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>16/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8785,19 +8306,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>28/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8832,19 +8349,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>28/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8879,189 +8392,185 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>28/33</t>
+          <t>0/33</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="inlineStr">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C161" s="5" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D161" s="5" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E161" s="5" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F161" s="5" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G161" s="5" t="inlineStr"/>
-      <c r="H161" s="5" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I161" s="5" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B162" s="5" t="inlineStr">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C162" s="5" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D162" s="5" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E162" s="5" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F162" s="5" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>12:05:00</t>
         </is>
       </c>
-      <c r="G162" s="5" t="inlineStr"/>
-      <c r="H162" s="5" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I162" s="5" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="inlineStr">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C163" s="5" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D163" s="5" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E163" s="5" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F163" s="5" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G163" s="5" t="inlineStr"/>
-      <c r="H163" s="5" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I163" s="5" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B164" s="5" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C164" s="5" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D164" s="5" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E164" s="5" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>17/01/2026</t>
         </is>
       </c>
-      <c r="F164" s="5" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G164" s="5" t="inlineStr"/>
-      <c r="H164" s="5" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>0/33</t>
         </is>
       </c>
-      <c r="I164" s="5" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9098,19 +8607,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9145,19 +8650,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9192,19 +8693,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G167" s="2" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9239,19 +8736,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9286,19 +8779,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G169" s="2" t="inlineStr"/>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9333,19 +8822,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G170" s="2" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9380,19 +8865,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G171" s="2" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9427,19 +8908,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9474,19 +8951,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>29/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9521,19 +8994,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>30/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9568,19 +9037,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9615,19 +9080,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G176" s="2" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9662,19 +9123,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9709,19 +9166,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>28/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9756,19 +9209,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9803,189 +9252,185 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B181" s="5" t="inlineStr">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C181" s="5" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D181" s="5" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E181" s="5" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F181" s="5" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G181" s="5" t="inlineStr"/>
-      <c r="H181" s="5" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I181" s="5" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B182" s="5" t="inlineStr">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C182" s="5" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D182" s="5" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E182" s="5" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F182" s="5" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>12:05:00</t>
         </is>
       </c>
-      <c r="G182" s="5" t="inlineStr"/>
-      <c r="H182" s="5" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I182" s="5" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C183" s="5" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D183" s="5" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E183" s="5" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F183" s="5" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G183" s="5" t="inlineStr"/>
-      <c r="H183" s="5" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I183" s="5" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B184" s="5" t="inlineStr">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C184" s="5" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D184" s="5" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E184" s="5" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>17/01/2026</t>
         </is>
       </c>
-      <c r="F184" s="5" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G184" s="5" t="inlineStr"/>
-      <c r="H184" s="5" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I184" s="5" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10022,19 +9467,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G185" s="2" t="inlineStr"/>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>0/27</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10069,19 +9510,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>0/27</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10116,19 +9553,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G187" s="2" t="inlineStr"/>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>0/27</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10163,19 +9596,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G188" s="2" t="inlineStr"/>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>0/27</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10210,19 +9639,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G189" s="2" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>27/27</t>
+          <t>0/27</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10257,19 +9682,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G190" s="2" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>24/27</t>
+          <t>0/27</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10304,19 +9725,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G191" s="2" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>0/27</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10351,103 +9768,99 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G192" s="2" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>0/27</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B193" s="5" t="inlineStr">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C193" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D193" s="5" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E193" s="5" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>06/01/2026</t>
         </is>
       </c>
-      <c r="F193" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G193" s="5" t="inlineStr"/>
-      <c r="H193" s="5" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>0/27</t>
         </is>
       </c>
-      <c r="I193" s="5" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B194" s="5" t="inlineStr">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C194" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D194" s="5" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E194" s="5" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="F194" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G194" s="5" t="inlineStr"/>
-      <c r="H194" s="5" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>0/27</t>
         </is>
       </c>
-      <c r="I194" s="5" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10484,19 +9897,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G195" s="2" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>27/27</t>
+          <t>0/27</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10531,19 +9940,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>0/27</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10578,60 +9983,56 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G197" s="2" t="inlineStr"/>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>0/27</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B198" s="5" t="inlineStr">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C198" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D198" s="5" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E198" s="5" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>19/01/2026</t>
         </is>
       </c>
-      <c r="F198" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G198" s="5" t="inlineStr"/>
-      <c r="H198" s="5" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>0/27</t>
         </is>
       </c>
-      <c r="I198" s="5" t="inlineStr">
+      <c r="I198" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10668,19 +10069,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G199" s="2" t="inlineStr"/>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>0/27</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10715,19 +10112,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G200" s="2" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>0/27</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10762,189 +10155,185 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G201" s="2" t="inlineStr"/>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>0/27</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B202" s="5" t="inlineStr">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C202" s="5" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D202" s="5" t="inlineStr">
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E202" s="5" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F202" s="5" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G202" s="5" t="inlineStr"/>
-      <c r="H202" s="5" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>0/27</t>
         </is>
       </c>
-      <c r="I202" s="5" t="inlineStr">
+      <c r="I202" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B203" s="5" t="inlineStr">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C203" s="5" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D203" s="5" t="inlineStr">
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E203" s="5" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F203" s="5" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>12:05:00</t>
         </is>
       </c>
-      <c r="G203" s="5" t="inlineStr"/>
-      <c r="H203" s="5" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>0/27</t>
         </is>
       </c>
-      <c r="I203" s="5" t="inlineStr">
+      <c r="I203" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B204" s="5" t="inlineStr">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C204" s="5" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D204" s="5" t="inlineStr">
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E204" s="5" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F204" s="5" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G204" s="5" t="inlineStr"/>
-      <c r="H204" s="5" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>0/27</t>
         </is>
       </c>
-      <c r="I204" s="5" t="inlineStr">
+      <c r="I204" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B205" s="5" t="inlineStr">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C205" s="5" t="inlineStr">
+      <c r="C205" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D205" s="5" t="inlineStr">
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E205" s="5" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>17/01/2026</t>
         </is>
       </c>
-      <c r="F205" s="5" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G205" s="5" t="inlineStr"/>
-      <c r="H205" s="5" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>0/27</t>
         </is>
       </c>
-      <c r="I205" s="5" t="inlineStr">
+      <c r="I205" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10981,19 +10370,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G206" s="2" t="inlineStr"/>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11028,19 +10413,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G207" s="2" t="inlineStr"/>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11075,19 +10456,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G208" s="2" t="inlineStr"/>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11122,19 +10499,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G209" s="2" t="inlineStr"/>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11169,19 +10542,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G210" s="2" t="inlineStr"/>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>28/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11216,19 +10585,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G211" s="2" t="inlineStr"/>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11263,19 +10628,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G212" s="2" t="inlineStr"/>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11310,103 +10671,99 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G213" s="2" t="inlineStr"/>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B214" s="5" t="inlineStr">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C214" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="5" t="inlineStr">
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E214" s="5" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>06/01/2026</t>
         </is>
       </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr"/>
-      <c r="H214" s="5" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I214" s="5" t="inlineStr">
+      <c r="I214" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B215" s="5" t="inlineStr">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C215" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="5" t="inlineStr">
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E215" s="5" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="F215" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr"/>
-      <c r="H215" s="5" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I215" s="5" t="inlineStr">
+      <c r="I215" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -11443,19 +10800,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G216" s="2" t="inlineStr"/>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11490,19 +10843,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G217" s="2" t="inlineStr"/>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11537,60 +10886,56 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G218" s="2" t="inlineStr"/>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B219" s="5" t="inlineStr">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C219" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D219" s="5" t="inlineStr">
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E219" s="5" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>19/01/2026</t>
         </is>
       </c>
-      <c r="F219" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G219" s="5" t="inlineStr"/>
-      <c r="H219" s="5" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I219" s="5" t="inlineStr">
+      <c r="I219" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -11627,19 +10972,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G220" s="2" t="inlineStr"/>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11674,19 +11015,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G221" s="2" t="inlineStr"/>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11721,189 +11058,185 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G222" s="2" t="inlineStr"/>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B223" s="5" t="inlineStr">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C223" s="5" t="inlineStr">
+      <c r="C223" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D223" s="5" t="inlineStr">
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E223" s="5" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F223" s="5" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G223" s="5" t="inlineStr"/>
-      <c r="H223" s="5" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I223" s="5" t="inlineStr">
+      <c r="I223" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B224" s="5" t="inlineStr">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C224" s="5" t="inlineStr">
+      <c r="C224" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D224" s="5" t="inlineStr">
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E224" s="5" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F224" s="5" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>12:05:00</t>
         </is>
       </c>
-      <c r="G224" s="5" t="inlineStr"/>
-      <c r="H224" s="5" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I224" s="5" t="inlineStr">
+      <c r="I224" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B225" s="5" t="inlineStr">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C225" s="5" t="inlineStr">
+      <c r="C225" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D225" s="5" t="inlineStr">
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E225" s="5" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F225" s="5" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G225" s="5" t="inlineStr"/>
-      <c r="H225" s="5" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I225" s="5" t="inlineStr">
+      <c r="I225" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B226" s="5" t="inlineStr">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C226" s="5" t="inlineStr">
+      <c r="C226" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D226" s="5" t="inlineStr">
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E226" s="5" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>17/01/2026</t>
         </is>
       </c>
-      <c r="F226" s="5" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G226" s="5" t="inlineStr"/>
-      <c r="H226" s="5" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I226" s="5" t="inlineStr">
+      <c r="I226" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -11940,19 +11273,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G227" s="2" t="inlineStr"/>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11987,19 +11316,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G228" s="2" t="inlineStr"/>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12034,19 +11359,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G229" s="2" t="inlineStr"/>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12081,19 +11402,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G230" s="2" t="inlineStr"/>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12128,19 +11445,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G231" s="2" t="inlineStr"/>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>29/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12175,19 +11488,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G232" s="2" t="inlineStr"/>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12222,19 +11531,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G233" s="2" t="inlineStr"/>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12269,103 +11574,99 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G234" s="2" t="inlineStr"/>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B235" s="5" t="inlineStr">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C235" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D235" s="5" t="inlineStr">
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E235" s="5" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>06/01/2026</t>
         </is>
       </c>
-      <c r="F235" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G235" s="5" t="inlineStr"/>
-      <c r="H235" s="5" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I235" s="5" t="inlineStr">
+      <c r="I235" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B236" s="5" t="inlineStr">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C236" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D236" s="5" t="inlineStr">
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E236" s="5" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="F236" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G236" s="5" t="inlineStr"/>
-      <c r="H236" s="5" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I236" s="5" t="inlineStr">
+      <c r="I236" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -12402,19 +11703,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G237" s="2" t="inlineStr"/>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12449,19 +11746,15 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G238" s="2" t="inlineStr"/>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12496,60 +11789,56 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com</t>
-        </is>
-      </c>
+      <c r="G239" s="2" t="inlineStr"/>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B240" s="5" t="inlineStr">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C240" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="inlineStr">
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E240" s="5" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>19/01/2026</t>
         </is>
       </c>
-      <c r="F240" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr"/>
-      <c r="H240" s="5" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I240" s="5" t="inlineStr">
+      <c r="I240" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -12586,19 +11875,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
+      <c r="G241" s="2" t="inlineStr"/>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12633,19 +11918,15 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G242" s="2" t="inlineStr"/>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12680,705 +11961,701 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr">
-        <is>
-          <t>dnasr281@gmail.com, System</t>
-        </is>
-      </c>
+      <c r="G243" s="2" t="inlineStr"/>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B244" s="5" t="inlineStr">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C244" s="5" t="inlineStr">
+      <c r="C244" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D244" s="5" t="inlineStr">
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E244" s="5" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F244" s="5" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G244" s="5" t="inlineStr"/>
-      <c r="H244" s="5" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I244" s="5" t="inlineStr">
+      <c r="I244" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B245" s="5" t="inlineStr">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C245" s="5" t="inlineStr">
+      <c r="C245" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D245" s="5" t="inlineStr">
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E245" s="5" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F245" s="5" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>12:05:00</t>
         </is>
       </c>
-      <c r="G245" s="5" t="inlineStr"/>
-      <c r="H245" s="5" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I245" s="5" t="inlineStr">
+      <c r="I245" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B246" s="5" t="inlineStr">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C246" s="5" t="inlineStr">
+      <c r="C246" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D246" s="5" t="inlineStr">
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E246" s="5" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="F246" s="5" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G246" s="5" t="inlineStr"/>
-      <c r="H246" s="5" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I246" s="5" t="inlineStr">
+      <c r="I246" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B247" s="5" t="inlineStr">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C247" s="5" t="inlineStr">
+      <c r="C247" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D247" s="5" t="inlineStr">
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E247" s="5" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>17/01/2026</t>
         </is>
       </c>
-      <c r="F247" s="5" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G247" s="5" t="inlineStr"/>
-      <c r="H247" s="5" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I247" s="5" t="inlineStr">
+      <c r="I247" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="5" t="inlineStr">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>Year5</t>
         </is>
       </c>
-      <c r="B248" s="5" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C248" s="5" t="inlineStr">
+      <c r="C248" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D248" s="5" t="inlineStr">
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E248" s="5" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F248" s="5" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>10:05:00</t>
         </is>
       </c>
-      <c r="G248" s="5" t="inlineStr"/>
-      <c r="H248" s="5" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I248" s="5" t="inlineStr">
+      <c r="I248" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="5" t="inlineStr">
+      <c r="A249" s="2" t="inlineStr">
         <is>
           <t>Year5</t>
         </is>
       </c>
-      <c r="B249" s="5" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C249" s="5" t="inlineStr">
+      <c r="C249" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D249" s="5" t="inlineStr">
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E249" s="5" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F249" s="5" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>10:05:00</t>
         </is>
       </c>
-      <c r="G249" s="5" t="inlineStr"/>
-      <c r="H249" s="5" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I249" s="5" t="inlineStr">
+      <c r="I249" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="5" t="inlineStr">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>Year5</t>
         </is>
       </c>
-      <c r="B250" s="5" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C250" s="5" t="inlineStr">
+      <c r="C250" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D250" s="5" t="inlineStr">
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E250" s="5" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F250" s="5" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>10:05:00</t>
         </is>
       </c>
-      <c r="G250" s="5" t="inlineStr"/>
-      <c r="H250" s="5" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I250" s="5" t="inlineStr">
+      <c r="I250" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="5" t="inlineStr">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>Year5</t>
         </is>
       </c>
-      <c r="B251" s="5" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C251" s="5" t="inlineStr">
+      <c r="C251" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D251" s="5" t="inlineStr">
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E251" s="5" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F251" s="5" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>10:05:00</t>
         </is>
       </c>
-      <c r="G251" s="5" t="inlineStr"/>
-      <c r="H251" s="5" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I251" s="5" t="inlineStr">
+      <c r="I251" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="5" t="inlineStr">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>Year5</t>
         </is>
       </c>
-      <c r="B252" s="5" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C252" s="5" t="inlineStr">
+      <c r="C252" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D252" s="5" t="inlineStr">
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E252" s="5" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F252" s="5" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>10:05:00</t>
         </is>
       </c>
-      <c r="G252" s="5" t="inlineStr"/>
-      <c r="H252" s="5" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I252" s="5" t="inlineStr">
+      <c r="I252" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="5" t="inlineStr">
+      <c r="A253" s="2" t="inlineStr">
         <is>
           <t>Year5</t>
         </is>
       </c>
-      <c r="B253" s="5" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C253" s="5" t="inlineStr">
+      <c r="C253" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D253" s="5" t="inlineStr">
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E253" s="5" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F253" s="5" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>10:05:00</t>
         </is>
       </c>
-      <c r="G253" s="5" t="inlineStr"/>
-      <c r="H253" s="5" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I253" s="5" t="inlineStr">
+      <c r="I253" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="5" t="inlineStr">
+      <c r="A254" s="2" t="inlineStr">
         <is>
           <t>Year5</t>
         </is>
       </c>
-      <c r="B254" s="5" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C254" s="5" t="inlineStr">
+      <c r="C254" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D254" s="5" t="inlineStr">
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E254" s="5" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F254" s="5" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>10:05:00</t>
         </is>
       </c>
-      <c r="G254" s="5" t="inlineStr"/>
-      <c r="H254" s="5" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I254" s="5" t="inlineStr">
+      <c r="I254" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="5" t="inlineStr">
+      <c r="A255" s="2" t="inlineStr">
         <is>
           <t>Year5</t>
         </is>
       </c>
-      <c r="B255" s="5" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C255" s="5" t="inlineStr">
+      <c r="C255" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D255" s="5" t="inlineStr">
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E255" s="5" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F255" s="5" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>10:05:00</t>
         </is>
       </c>
-      <c r="G255" s="5" t="inlineStr"/>
-      <c r="H255" s="5" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I255" s="5" t="inlineStr">
+      <c r="I255" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="5" t="inlineStr">
+      <c r="A256" s="2" t="inlineStr">
         <is>
           <t>Year5</t>
         </is>
       </c>
-      <c r="B256" s="5" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C256" s="5" t="inlineStr">
+      <c r="C256" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D256" s="5" t="inlineStr">
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E256" s="5" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F256" s="5" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>10:05:00</t>
         </is>
       </c>
-      <c r="G256" s="5" t="inlineStr"/>
-      <c r="H256" s="5" t="inlineStr">
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I256" s="5" t="inlineStr">
+      <c r="I256" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="5" t="inlineStr">
+      <c r="A257" s="2" t="inlineStr">
         <is>
           <t>Year5</t>
         </is>
       </c>
-      <c r="B257" s="5" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C257" s="5" t="inlineStr">
+      <c r="C257" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D257" s="5" t="inlineStr">
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E257" s="5" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F257" s="5" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>10:05:00</t>
         </is>
       </c>
-      <c r="G257" s="5" t="inlineStr"/>
-      <c r="H257" s="5" t="inlineStr">
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I257" s="5" t="inlineStr">
+      <c r="I257" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="5" t="inlineStr">
+      <c r="A258" s="2" t="inlineStr">
         <is>
           <t>Year5</t>
         </is>
       </c>
-      <c r="B258" s="5" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C258" s="5" t="inlineStr">
+      <c r="C258" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D258" s="5" t="inlineStr">
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E258" s="5" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F258" s="5" t="inlineStr">
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>10:05:00</t>
         </is>
       </c>
-      <c r="G258" s="5" t="inlineStr"/>
-      <c r="H258" s="5" t="inlineStr">
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I258" s="5" t="inlineStr">
+      <c r="I258" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="5" t="inlineStr">
+      <c r="A259" s="2" t="inlineStr">
         <is>
           <t>Year5</t>
         </is>
       </c>
-      <c r="B259" s="5" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C259" s="5" t="inlineStr">
+      <c r="C259" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D259" s="5" t="inlineStr">
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E259" s="5" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>03/01/2026</t>
         </is>
       </c>
-      <c r="F259" s="5" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>10:05:00</t>
         </is>
       </c>
-      <c r="G259" s="5" t="inlineStr"/>
-      <c r="H259" s="5" t="inlineStr">
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I259" s="5" t="inlineStr">
+      <c r="I259" s="2" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -571,11 +571,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -623,11 +619,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>18/28</t>
@@ -680,11 +672,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -735,11 +723,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -790,11 +774,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>19/28</t>
@@ -845,11 +825,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>26/28</t>
@@ -900,11 +876,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -955,11 +927,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -1012,11 +980,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -1069,11 +1033,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>26/28</t>
@@ -1116,11 +1076,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>19/28</t>
@@ -1163,11 +1119,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -1215,11 +1167,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>16/28</t>
@@ -1307,11 +1255,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>22/28</t>
@@ -1389,11 +1333,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>22/28</t>
@@ -1471,11 +1411,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>22/28</t>
@@ -1865,11 +1801,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>20/31</t>
@@ -1947,11 +1879,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>16/31</t>
@@ -2029,11 +1957,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>26/31</t>
@@ -2111,11 +2035,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>24/31</t>
@@ -2193,11 +2113,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>29/31</t>
@@ -2275,11 +2191,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>22/31</t>
@@ -2357,11 +2269,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>27/31</t>
@@ -2439,11 +2347,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>24/31</t>
@@ -2677,11 +2581,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>26/31</t>
@@ -2759,11 +2659,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>27/31</t>
@@ -2841,11 +2737,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -3001,11 +2893,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>23/31</t>
@@ -3083,11 +2971,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -3165,11 +3049,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -3439,11 +3319,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>6/18</t>
@@ -3501,11 +3377,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>7/18</t>
@@ -3563,11 +3435,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>14/18</t>
@@ -3625,11 +3493,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>11/18</t>
@@ -3672,11 +3536,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>13/18</t>
@@ -3719,11 +3579,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>12/18</t>
@@ -3766,11 +3622,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>13/18</t>
@@ -3813,11 +3665,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>14/18</t>
@@ -3946,11 +3794,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t>17/18</t>
@@ -3993,11 +3837,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>16/18</t>
@@ -4040,11 +3880,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t>14/18</t>
@@ -4130,11 +3966,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t>8/18</t>
@@ -4177,11 +4009,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>12/18</t>
@@ -4224,11 +4052,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t>12/18</t>
@@ -4443,11 +4267,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>18/21</t>
@@ -4490,11 +4310,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>18/21</t>
@@ -4537,11 +4353,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t>14/21</t>
@@ -4584,11 +4396,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t>20/21</t>
@@ -4631,11 +4439,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>17/21</t>
@@ -4678,11 +4482,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>19/21</t>
@@ -4725,11 +4525,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t>15/21</t>
@@ -4772,11 +4568,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t>17/21</t>
@@ -4905,11 +4697,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>20/21</t>
@@ -4952,11 +4740,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t>16/21</t>
@@ -4999,11 +4783,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>11/21</t>
@@ -5089,11 +4869,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
           <t>17/21</t>
@@ -5136,11 +4912,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
           <t>18/21</t>
@@ -5183,11 +4955,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t>18/21</t>
@@ -5402,11 +5170,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t>30/31</t>
@@ -5449,11 +5213,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>29/31</t>
@@ -5496,11 +5256,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t>29/31</t>
@@ -5543,11 +5299,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>30/31</t>
@@ -5590,11 +5342,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
           <t>25/31</t>
@@ -5637,11 +5385,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t>28/31</t>
@@ -5684,11 +5428,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
           <t>28/31</t>
@@ -5731,11 +5471,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t>29/31</t>
@@ -5778,11 +5514,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
           <t>30/31</t>
@@ -5825,11 +5557,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
           <t>31/31</t>
@@ -5872,11 +5600,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
           <t>17/31</t>
@@ -5919,11 +5643,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
           <t>21/31</t>
@@ -5966,11 +5686,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
           <t>14/31</t>
@@ -6013,11 +5729,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
           <t>23/31</t>
@@ -6060,11 +5772,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
           <t>25/31</t>
@@ -6107,11 +5815,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
           <t>25/31</t>
@@ -6326,11 +6030,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -6373,11 +6073,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -6420,11 +6116,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
           <t>27/28</t>
@@ -6467,11 +6159,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
           <t>27/28</t>
@@ -6514,11 +6202,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -6561,11 +6245,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
           <t>28/28</t>
@@ -6608,11 +6288,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
           <t>28/28</t>
@@ -6655,11 +6331,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -6702,11 +6374,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -6749,11 +6417,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t>27/28</t>
@@ -6796,11 +6460,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -6843,11 +6503,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
           <t>18/28</t>
@@ -6890,11 +6546,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
           <t>8/28</t>
@@ -6937,11 +6589,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
           <t>26/28</t>
@@ -6984,11 +6632,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -7031,11 +6675,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -7250,11 +6890,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -7297,11 +6933,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
           <t>26/29</t>
@@ -7344,11 +6976,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -7391,11 +7019,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -7438,11 +7062,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
           <t>27/29</t>
@@ -7485,11 +7105,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -7532,11 +7148,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -7579,11 +7191,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -7626,11 +7234,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
           <t>28/29</t>
@@ -7673,11 +7277,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
           <t>28/29</t>
@@ -7720,11 +7320,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
           <t>15/29</t>
@@ -7767,11 +7363,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -7814,11 +7406,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
           <t>19/29</t>
@@ -7861,11 +7449,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
           <t>27/29</t>
@@ -7908,11 +7492,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
@@ -7955,11 +7535,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
@@ -8174,11 +7750,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
           <t>32/33</t>
@@ -8221,11 +7793,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
           <t>29/33</t>
@@ -8268,11 +7836,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
           <t>31/33</t>
@@ -8315,11 +7879,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
           <t>32/33</t>
@@ -8362,11 +7922,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
           <t>30/33</t>
@@ -8409,11 +7965,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
           <t>32/33</t>
@@ -8456,11 +8008,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
           <t>33/33</t>
@@ -8503,11 +8051,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
           <t>28/33</t>
@@ -8550,11 +8094,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
           <t>30/33</t>
@@ -8597,11 +8137,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
           <t>33/33</t>
@@ -8644,11 +8180,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
           <t>26/33</t>
@@ -8691,11 +8223,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
           <t>22/33</t>
@@ -8738,11 +8266,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
           <t>16/33</t>
@@ -8785,11 +8309,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
           <t>28/33</t>
@@ -8832,11 +8352,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
           <t>28/33</t>
@@ -8879,11 +8395,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
           <t>28/33</t>
@@ -9098,11 +8610,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -9145,11 +8653,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -9192,11 +8696,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G167" s="2" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr">
         <is>
           <t>25/30</t>
@@ -9239,11 +8739,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -9286,11 +8782,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G169" s="2" t="inlineStr"/>
       <c r="H169" s="2" t="inlineStr">
         <is>
           <t>21/30</t>
@@ -9333,11 +8825,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G170" s="2" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr">
         <is>
           <t>25/30</t>
@@ -9380,11 +8868,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G171" s="2" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
           <t>27/30</t>
@@ -9427,11 +8911,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -9474,11 +8954,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
           <t>29/30</t>
@@ -9521,11 +8997,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
           <t>30/30</t>
@@ -9568,11 +9040,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -9615,11 +9083,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G176" s="2" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
           <t>19/30</t>
@@ -9662,11 +9126,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
           <t>19/30</t>
@@ -9709,11 +9169,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
           <t>28/30</t>
@@ -9756,11 +9212,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -9803,11 +9255,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -10022,11 +9470,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G185" s="2" t="inlineStr"/>
       <c r="H185" s="2" t="inlineStr">
         <is>
           <t>14/27</t>
@@ -10069,11 +9513,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr">
         <is>
           <t>12/27</t>
@@ -10116,11 +9556,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G187" s="2" t="inlineStr"/>
       <c r="H187" s="2" t="inlineStr">
         <is>
           <t>17/27</t>
@@ -10163,11 +9599,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G188" s="2" t="inlineStr"/>
       <c r="H188" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -10210,11 +9642,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G189" s="2" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr">
         <is>
           <t>27/27</t>
@@ -10257,11 +9685,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G190" s="2" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -10304,11 +9728,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G191" s="2" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -10351,11 +9771,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G192" s="2" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr">
         <is>
           <t>18/27</t>
@@ -10484,11 +9900,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G195" s="2" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr">
         <is>
           <t>27/27</t>
@@ -10531,11 +9943,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr">
         <is>
           <t>19/27</t>
@@ -10578,11 +9986,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G197" s="2" t="inlineStr"/>
       <c r="H197" s="2" t="inlineStr">
         <is>
           <t>19/27</t>
@@ -10668,11 +10072,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G199" s="2" t="inlineStr"/>
       <c r="H199" s="2" t="inlineStr">
         <is>
           <t>16/27</t>
@@ -10715,11 +10115,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G200" s="2" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -10762,11 +10158,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G201" s="2" t="inlineStr"/>
       <c r="H201" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -10981,11 +10373,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G206" s="2" t="inlineStr"/>
       <c r="H206" s="2" t="inlineStr">
         <is>
           <t>20/29</t>
@@ -11028,11 +10416,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G207" s="2" t="inlineStr"/>
       <c r="H207" s="2" t="inlineStr">
         <is>
           <t>15/29</t>
@@ -11075,11 +10459,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G208" s="2" t="inlineStr"/>
       <c r="H208" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -11122,11 +10502,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G209" s="2" t="inlineStr"/>
       <c r="H209" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -11169,11 +10545,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G210" s="2" t="inlineStr"/>
       <c r="H210" s="2" t="inlineStr">
         <is>
           <t>28/29</t>
@@ -11216,11 +10588,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G211" s="2" t="inlineStr"/>
       <c r="H211" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -11263,11 +10631,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G212" s="2" t="inlineStr"/>
       <c r="H212" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
@@ -11310,11 +10674,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G213" s="2" t="inlineStr"/>
       <c r="H213" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -11443,11 +10803,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G216" s="2" t="inlineStr"/>
       <c r="H216" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -11490,11 +10846,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G217" s="2" t="inlineStr"/>
       <c r="H217" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -11537,11 +10889,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G218" s="2" t="inlineStr"/>
       <c r="H218" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -11627,11 +10975,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G220" s="2" t="inlineStr"/>
       <c r="H220" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -11674,11 +11018,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G221" s="2" t="inlineStr"/>
       <c r="H221" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -11721,11 +11061,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G222" s="2" t="inlineStr"/>
       <c r="H222" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -11940,11 +11276,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G227" s="2" t="inlineStr"/>
       <c r="H227" s="2" t="inlineStr">
         <is>
           <t>14/29</t>
@@ -11987,11 +11319,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G228" s="2" t="inlineStr"/>
       <c r="H228" s="2" t="inlineStr">
         <is>
           <t>12/29</t>
@@ -12034,11 +11362,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G229" s="2" t="inlineStr"/>
       <c r="H229" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -12081,11 +11405,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G230" s="2" t="inlineStr"/>
       <c r="H230" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -12128,11 +11448,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G231" s="2" t="inlineStr"/>
       <c r="H231" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -12175,11 +11491,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G232" s="2" t="inlineStr"/>
       <c r="H232" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -12222,11 +11534,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G233" s="2" t="inlineStr"/>
       <c r="H233" s="2" t="inlineStr">
         <is>
           <t>19/29</t>
@@ -12269,11 +11577,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G234" s="2" t="inlineStr"/>
       <c r="H234" s="2" t="inlineStr">
         <is>
           <t>27/29</t>
@@ -12402,11 +11706,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G237" s="2" t="inlineStr"/>
       <c r="H237" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -12449,11 +11749,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G238" s="2" t="inlineStr"/>
       <c r="H238" s="2" t="inlineStr">
         <is>
           <t>25/29</t>
@@ -12496,11 +11792,7 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G239" s="2" t="inlineStr"/>
       <c r="H239" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -12586,11 +11878,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G241" s="2" t="inlineStr"/>
       <c r="H241" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -12633,11 +11921,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G242" s="2" t="inlineStr"/>
       <c r="H242" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -12680,11 +11964,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G243" s="2" t="inlineStr"/>
       <c r="H243" s="2" t="inlineStr">
         <is>
           <t>24/29</t>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -571,7 +571,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -619,7 +623,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>18/28</t>
@@ -672,7 +680,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -723,7 +735,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -774,7 +790,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>19/28</t>
@@ -825,7 +845,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>26/28</t>
@@ -876,7 +900,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -927,7 +955,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -980,7 +1012,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -1033,7 +1069,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>26/28</t>
@@ -1076,7 +1116,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>19/28</t>
@@ -1119,7 +1163,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -1167,7 +1215,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>16/28</t>
@@ -1255,7 +1307,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>22/28</t>
@@ -1333,7 +1389,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>22/28</t>
@@ -1411,7 +1471,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>22/28</t>
@@ -1801,7 +1865,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>20/31</t>
@@ -1879,7 +1947,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>16/31</t>
@@ -1957,7 +2029,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>26/31</t>
@@ -2035,7 +2111,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>24/31</t>
@@ -2113,7 +2193,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>29/31</t>
@@ -2191,7 +2275,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>22/31</t>
@@ -2269,7 +2357,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>27/31</t>
@@ -2347,7 +2439,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>24/31</t>
@@ -2581,7 +2677,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>26/31</t>
@@ -2659,7 +2759,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>27/31</t>
@@ -2737,7 +2841,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -2893,7 +3001,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>23/31</t>
@@ -2971,7 +3083,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -3049,7 +3165,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -3319,7 +3439,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>6/18</t>
@@ -3377,7 +3501,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>7/18</t>
@@ -3435,7 +3563,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>14/18</t>
@@ -3493,7 +3625,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>11/18</t>
@@ -3536,7 +3672,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>13/18</t>
@@ -3579,7 +3719,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>12/18</t>
@@ -3622,7 +3766,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>13/18</t>
@@ -3665,7 +3813,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>14/18</t>
@@ -3794,7 +3946,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t>17/18</t>
@@ -3837,7 +3993,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>16/18</t>
@@ -3880,7 +4040,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t>14/18</t>
@@ -3966,7 +4130,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t>8/18</t>
@@ -4009,7 +4177,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>12/18</t>
@@ -4052,7 +4224,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t>12/18</t>
@@ -4267,7 +4443,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>18/21</t>
@@ -4310,7 +4490,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>18/21</t>
@@ -4353,7 +4537,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t>14/21</t>
@@ -4396,7 +4584,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t>20/21</t>
@@ -4439,7 +4631,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>17/21</t>
@@ -4482,7 +4678,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>19/21</t>
@@ -4525,7 +4725,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t>15/21</t>
@@ -4568,7 +4772,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t>17/21</t>
@@ -4697,7 +4905,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>20/21</t>
@@ -4740,7 +4952,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t>16/21</t>
@@ -4783,7 +4999,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>11/21</t>
@@ -4869,7 +5089,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
           <t>17/21</t>
@@ -4912,7 +5136,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
           <t>18/21</t>
@@ -4955,7 +5183,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t>18/21</t>
@@ -5170,7 +5402,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t>30/31</t>
@@ -5213,7 +5449,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>29/31</t>
@@ -5256,7 +5496,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t>29/31</t>
@@ -5299,7 +5543,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>30/31</t>
@@ -5342,7 +5590,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
           <t>25/31</t>
@@ -5385,7 +5637,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t>28/31</t>
@@ -5428,7 +5684,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
           <t>28/31</t>
@@ -5471,7 +5731,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t>29/31</t>
@@ -5514,7 +5778,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
           <t>30/31</t>
@@ -5557,7 +5825,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
           <t>31/31</t>
@@ -5600,7 +5872,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
           <t>17/31</t>
@@ -5643,7 +5919,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
           <t>21/31</t>
@@ -5686,7 +5966,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
           <t>14/31</t>
@@ -5729,7 +6013,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
           <t>23/31</t>
@@ -5772,7 +6060,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
           <t>25/31</t>
@@ -5815,7 +6107,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
           <t>25/31</t>
@@ -6030,7 +6326,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -6073,7 +6373,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -6116,7 +6420,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
           <t>27/28</t>
@@ -6159,7 +6467,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
           <t>27/28</t>
@@ -6202,7 +6514,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -6245,7 +6561,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
           <t>28/28</t>
@@ -6288,7 +6608,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
           <t>28/28</t>
@@ -6331,7 +6655,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -6374,7 +6702,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -6417,7 +6749,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t>27/28</t>
@@ -6460,7 +6796,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -6503,7 +6843,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
           <t>18/28</t>
@@ -6546,7 +6890,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
           <t>8/28</t>
@@ -6589,7 +6937,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
           <t>26/28</t>
@@ -6632,7 +6984,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -6675,7 +7031,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -6890,7 +7250,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -6933,7 +7297,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
           <t>26/29</t>
@@ -6976,7 +7344,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -7019,7 +7391,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -7062,7 +7438,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
           <t>27/29</t>
@@ -7105,7 +7485,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -7148,7 +7532,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -7191,7 +7579,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -7234,7 +7626,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
           <t>28/29</t>
@@ -7277,7 +7673,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
           <t>28/29</t>
@@ -7320,7 +7720,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
           <t>15/29</t>
@@ -7363,7 +7767,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -7406,7 +7814,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
           <t>19/29</t>
@@ -7449,7 +7861,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
           <t>27/29</t>
@@ -7492,7 +7908,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
@@ -7535,7 +7955,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
@@ -7750,7 +8174,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
           <t>32/33</t>
@@ -7793,7 +8221,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
           <t>29/33</t>
@@ -7836,7 +8268,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
           <t>31/33</t>
@@ -7879,7 +8315,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
           <t>32/33</t>
@@ -7922,7 +8362,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
           <t>30/33</t>
@@ -7965,7 +8409,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
           <t>32/33</t>
@@ -8008,7 +8456,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
           <t>33/33</t>
@@ -8051,7 +8503,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
           <t>28/33</t>
@@ -8094,7 +8550,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
           <t>30/33</t>
@@ -8137,7 +8597,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
           <t>33/33</t>
@@ -8180,7 +8644,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
           <t>26/33</t>
@@ -8223,7 +8691,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
           <t>22/33</t>
@@ -8266,7 +8738,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
           <t>16/33</t>
@@ -8309,7 +8785,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
           <t>28/33</t>
@@ -8352,7 +8832,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
           <t>28/33</t>
@@ -8395,7 +8879,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
           <t>28/33</t>
@@ -8610,7 +9098,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -8653,7 +9145,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -8696,7 +9192,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
           <t>25/30</t>
@@ -8739,7 +9239,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -8782,7 +9286,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
           <t>21/30</t>
@@ -8825,7 +9333,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
           <t>25/30</t>
@@ -8868,7 +9380,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
           <t>27/30</t>
@@ -8911,7 +9427,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -8954,7 +9474,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
           <t>29/30</t>
@@ -8997,7 +9521,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
           <t>30/30</t>
@@ -9040,7 +9568,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -9083,7 +9615,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
           <t>19/30</t>
@@ -9126,7 +9662,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
           <t>19/30</t>
@@ -9169,7 +9709,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
           <t>28/30</t>
@@ -9212,7 +9756,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -9255,7 +9803,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -9470,7 +10022,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
           <t>14/27</t>
@@ -9513,7 +10069,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
           <t>12/27</t>
@@ -9556,7 +10116,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
           <t>17/27</t>
@@ -9599,7 +10163,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -9642,7 +10210,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
           <t>27/27</t>
@@ -9685,7 +10257,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -9728,7 +10304,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -9771,7 +10351,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
           <t>18/27</t>
@@ -9900,7 +10484,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
           <t>27/27</t>
@@ -9943,7 +10531,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
           <t>19/27</t>
@@ -9986,7 +10578,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
           <t>19/27</t>
@@ -10072,7 +10668,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
           <t>16/27</t>
@@ -10115,7 +10715,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -10158,7 +10762,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -10373,7 +10981,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
           <t>20/29</t>
@@ -10416,7 +11028,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
           <t>15/29</t>
@@ -10459,7 +11075,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -10502,7 +11122,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -10545,7 +11169,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
           <t>28/29</t>
@@ -10588,7 +11216,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr"/>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -10631,7 +11263,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr"/>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
@@ -10674,7 +11310,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -10803,7 +11443,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -10846,7 +11490,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -10889,7 +11537,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr"/>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -10975,7 +11627,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -11018,7 +11674,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr"/>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -11061,7 +11721,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr"/>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -11276,7 +11940,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr"/>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
           <t>14/29</t>
@@ -11319,7 +11987,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr"/>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
           <t>12/29</t>
@@ -11362,7 +12034,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr"/>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -11405,7 +12081,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr"/>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -11448,7 +12128,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr"/>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -11491,7 +12175,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr"/>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -11534,7 +12222,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr"/>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
           <t>19/29</t>
@@ -11577,7 +12269,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr"/>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
           <t>27/29</t>
@@ -11706,7 +12402,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr"/>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -11749,7 +12449,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr"/>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
           <t>25/29</t>
@@ -11792,7 +12496,11 @@
           <t>12:00:00</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr"/>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -11878,7 +12586,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr"/>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -11921,7 +12633,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr"/>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -11964,7 +12680,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr"/>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
